--- a/artfynd/A 7349-2025 artfynd.xlsx
+++ b/artfynd/A 7349-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,6 +786,365 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122923641</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56691</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Väst Örkyttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>373021</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6626086</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Satt I trädtoppar</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122923475</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Väst Örkyttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>372832</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6625991</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122923464</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57631</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Väst Örkyttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>372754</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6625917</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7349-2025 artfynd.xlsx
+++ b/artfynd/A 7349-2025 artfynd.xlsx
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122923475</v>
+        <v>122923464</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,21 +928,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -968,13 +968,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372832</v>
+        <v>372754</v>
       </c>
       <c r="R4" t="n">
-        <v>6625991</v>
+        <v>6625917</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122923464</v>
+        <v>122923475</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,21 +1046,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1086,13 +1086,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372754</v>
+        <v>372832</v>
       </c>
       <c r="R5" t="n">
-        <v>6625917</v>
+        <v>6625991</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 7349-2025 artfynd.xlsx
+++ b/artfynd/A 7349-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1146,6 +1146,139 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123083392</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>väst Örkyttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>372563</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6625910</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Lockades att trumma med hjälp av ljuduppspelning</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7349-2025 artfynd.xlsx
+++ b/artfynd/A 7349-2025 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122923641</v>
+        <v>122923464</v>
       </c>
       <c r="B3" t="n">
-        <v>56691</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,36 +801,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>373021</v>
+        <v>372754</v>
       </c>
       <c r="R3" t="n">
-        <v>6626086</v>
+        <v>6625917</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,11 +881,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Satt I trädtoppar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122923464</v>
+        <v>122923475</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -968,13 +963,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372754</v>
+        <v>372832</v>
       </c>
       <c r="R4" t="n">
-        <v>6625917</v>
+        <v>6625991</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1030,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122923475</v>
+        <v>122923641</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>56691</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,20 +1037,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>102613</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1065,13 +1060,13 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1086,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372832</v>
+        <v>373021</v>
       </c>
       <c r="R5" t="n">
-        <v>6625991</v>
+        <v>6626086</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1122,6 +1117,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Satt I trädtoppar</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 7349-2025 artfynd.xlsx
+++ b/artfynd/A 7349-2025 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122923464</v>
+        <v>122923641</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>56691</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,36 +801,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372754</v>
+        <v>373021</v>
       </c>
       <c r="R3" t="n">
-        <v>6625917</v>
+        <v>6626086</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,6 +881,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Satt I trädtoppar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122923475</v>
+        <v>122923464</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +928,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -963,13 +968,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372832</v>
+        <v>372754</v>
       </c>
       <c r="R4" t="n">
-        <v>6625991</v>
+        <v>6625917</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1025,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122923641</v>
+        <v>122923475</v>
       </c>
       <c r="B5" t="n">
-        <v>56691</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,20 +1042,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1060,13 +1065,13 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1081,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>373021</v>
+        <v>372832</v>
       </c>
       <c r="R5" t="n">
-        <v>6626086</v>
+        <v>6625991</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1117,11 +1122,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Satt I trädtoppar</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 7349-2025 artfynd.xlsx
+++ b/artfynd/A 7349-2025 artfynd.xlsx
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122923464</v>
+        <v>122923475</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,21 +928,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -968,13 +968,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372754</v>
+        <v>372832</v>
       </c>
       <c r="R4" t="n">
-        <v>6625917</v>
+        <v>6625991</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122923475</v>
+        <v>122923464</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,21 +1046,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1086,13 +1086,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372832</v>
+        <v>372754</v>
       </c>
       <c r="R5" t="n">
-        <v>6625991</v>
+        <v>6625917</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 7349-2025 artfynd.xlsx
+++ b/artfynd/A 7349-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122904432</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122923641</v>
+        <v>122923464</v>
       </c>
       <c r="B3" t="n">
-        <v>56691</v>
+        <v>57634</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,36 +801,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>373021</v>
+        <v>372754</v>
       </c>
       <c r="R3" t="n">
-        <v>6626086</v>
+        <v>6625917</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,11 +881,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Satt I trädtoppar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +910,7 @@
         <v>122923475</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1030,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122923464</v>
+        <v>122923641</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
+        <v>56694</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,36 +1037,36 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>102613</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1086,13 +1081,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372754</v>
+        <v>373021</v>
       </c>
       <c r="R5" t="n">
-        <v>6625917</v>
+        <v>6626086</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,6 +1117,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Satt I trädtoppar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,7 +1151,7 @@
         <v>123083392</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 7349-2025 artfynd.xlsx
+++ b/artfynd/A 7349-2025 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122923464</v>
+        <v>122923641</v>
       </c>
       <c r="B3" t="n">
-        <v>57634</v>
+        <v>56694</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,36 +801,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372754</v>
+        <v>373021</v>
       </c>
       <c r="R3" t="n">
-        <v>6625917</v>
+        <v>6626086</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,6 +881,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Satt I trädtoppar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1025,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122923641</v>
+        <v>122923464</v>
       </c>
       <c r="B5" t="n">
-        <v>56694</v>
+        <v>57634</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,36 +1042,36 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1081,13 +1086,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>373021</v>
+        <v>372754</v>
       </c>
       <c r="R5" t="n">
-        <v>6626086</v>
+        <v>6625917</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1117,11 +1122,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Satt I trädtoppar</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 7349-2025 artfynd.xlsx
+++ b/artfynd/A 7349-2025 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122923641</v>
+        <v>122923475</v>
       </c>
       <c r="B3" t="n">
-        <v>56694</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,20 +801,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -824,13 +824,13 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>373021</v>
+        <v>372832</v>
       </c>
       <c r="R3" t="n">
-        <v>6626086</v>
+        <v>6625991</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,11 +881,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Satt I trädtoppar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122923475</v>
+        <v>122923641</v>
       </c>
       <c r="B4" t="n">
-        <v>57497</v>
+        <v>56694</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,20 +919,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -947,13 +942,13 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -968,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372832</v>
+        <v>373021</v>
       </c>
       <c r="R4" t="n">
-        <v>6625991</v>
+        <v>6626086</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1004,6 +999,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Satt I trädtoppar</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 7349-2025 artfynd.xlsx
+++ b/artfynd/A 7349-2025 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122923641</v>
+        <v>122923475</v>
       </c>
       <c r="B3" t="n">
-        <v>56694</v>
+        <v>57503</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,20 +801,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -824,13 +824,13 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>373021</v>
+        <v>372832</v>
       </c>
       <c r="R3" t="n">
-        <v>6626086</v>
+        <v>6625991</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,11 +881,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Satt I trädtoppar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122923475</v>
+        <v>122923641</v>
       </c>
       <c r="B4" t="n">
-        <v>57497</v>
+        <v>56700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,20 +919,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -947,13 +942,13 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -968,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372832</v>
+        <v>373021</v>
       </c>
       <c r="R4" t="n">
-        <v>6625991</v>
+        <v>6626086</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1004,6 +999,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Satt I trädtoppar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,7 +1033,7 @@
         <v>122923464</v>
       </c>
       <c r="B5" t="n">
-        <v>57634</v>
+        <v>57640</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>123083392</v>
       </c>
       <c r="B6" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 7349-2025 artfynd.xlsx
+++ b/artfynd/A 7349-2025 artfynd.xlsx
@@ -1151,7 +1151,7 @@
         <v>123083392</v>
       </c>
       <c r="B6" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 7349-2025 artfynd.xlsx
+++ b/artfynd/A 7349-2025 artfynd.xlsx
@@ -1151,7 +1151,7 @@
         <v>123083392</v>
       </c>
       <c r="B6" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 7349-2025 artfynd.xlsx
+++ b/artfynd/A 7349-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1279,6 +1279,120 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124778957</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>V Örkyttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>372941</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6626051</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7349-2025 artfynd.xlsx
+++ b/artfynd/A 7349-2025 artfynd.xlsx
@@ -1284,7 +1284,7 @@
         <v>124778957</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
